--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/04_applications_systems.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/04_applications_systems.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rb7042b1950db45cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rf81f6fc5dfea4671"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R10ca947dc1704cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R90bf7c39975848ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Re2bf12d541be461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R7523c4a25e1c46cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Platform Segments" sheetId="7" r:id="Rbad9fdd2cb4248e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Case Boundary" sheetId="8" r:id="R4368bd28fed0414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rcad7e48027614f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R1f8253b49e3d4c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rda2bcfcad92d4cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6df18de698004e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R561f17af9ece499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rbc7cd3f894c244d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Platform Segments" sheetId="7" r:id="R69745dca19574684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use Case Boundary" sheetId="8" r:id="R41bd5912eed540e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -653,7 +653,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re91a3b646a1147f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f93eb4fab794721"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -844,7 +844,7 @@
         <x:v>Chief Strategy Officer / Executive Office Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P6" s="80" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Executive Office Workflow Platform (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q6" s="41" t="str">
         <x:v>High</x:v>
@@ -897,7 +897,7 @@
         <x:v>Chief Strategy Officer / Executive Office Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P7" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Executive Office Analytics Mart (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q7" s="43" t="str">
         <x:v>Medium</x:v>
@@ -950,7 +950,7 @@
         <x:v>Chief Strategy Officer / Executive Office Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P8" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Executive Office Reporting Workspace (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q8" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1003,7 +1003,7 @@
         <x:v>CMO / Epic Hyperspace technology owner</x:v>
       </x:c>
       <x:c r="P9" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Epic Hyperspace (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q9" s="43" t="str">
         <x:v>High</x:v>
@@ -1056,7 +1056,7 @@
         <x:v>CMO / Epic Clarity technology owner</x:v>
       </x:c>
       <x:c r="P10" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Epic Clarity (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q10" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>CMO / Epic Caboodle technology owner</x:v>
       </x:c>
       <x:c r="P11" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Epic Caboodle (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q11" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1162,7 +1162,7 @@
         <x:v>CMO / Epic FHIR Gateway technology owner</x:v>
       </x:c>
       <x:c r="P12" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Epic FHIR Gateway (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q12" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>Health Plan COO / Claims Administration Platform technology owner</x:v>
       </x:c>
       <x:c r="P13" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Claims Administration Platform (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q13" s="43" t="str">
         <x:v>High</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>Health Plan COO / Claims Payment Rules Engine technology owner</x:v>
       </x:c>
       <x:c r="P14" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Claims Payment Rules Engine (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q14" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>Health Plan COO / Claims Inquiry CRM Adapter technology owner</x:v>
       </x:c>
       <x:c r="P15" s="81" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Inquiry CRM Adapter (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q15" s="43" t="str">
         <x:v>Medium</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P16" s="82" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Eligibility and Benefits Workflow Platform (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q16" s="45" t="str">
         <x:v>High</x:v>
@@ -1427,7 +1427,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Eligibility and Benefits Analytics Mart (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q17" t="str">
         <x:v>Medium</x:v>
@@ -1480,7 +1480,7 @@
         <x:v>VP Benefits Operations / Eligibility and Benefits Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits Reporting Workspace (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q18" t="str">
         <x:v>Medium</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Prior Authorization and UM Workflow Platform (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q19" t="str">
         <x:v>High</x:v>
@@ -1586,7 +1586,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM Analytics Mart (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q20" t="str">
         <x:v>Medium</x:v>
@@ -1639,7 +1639,7 @@
         <x:v>VP Utilization Management / Prior Authorization and UM Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Prior Authorization and UM Reporting Workspace (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q21" t="str">
         <x:v>Medium</x:v>
@@ -1662,7 +1662,7 @@
         <x:v>Contact center</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="G22" t="str">
         <x:v>Contact Center and Member Service core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -1677,22 +1677,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>384 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: First contact resolution for claims-status calls; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>20 interfaces or reports; 5 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; performance issue: CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>Contact Center Member Service Operational Dataset; Contact Center Member Service Analytics Mart; Contact Center Member Service Dashboard Inventory; Contact Center Member Service Data Quality Rules</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Upstream: Genesys Cloud Contact Center; downstream: Contact Center Member Service Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Chief Experience Officer / Genesys Cloud Contact Center technology owner</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Genesys Cloud Contact Center (record 17) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q22" t="str">
         <x:v>High</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>CRM</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="G23" t="str">
         <x:v>Contact Center and Member Service core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -1730,22 +1730,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>559 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: After-call work minutes per agent shift; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>50 interfaces or reports; 13 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.; performance issue: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>Contact Center Member Service Operational Dataset; Contact Center Member Service Analytics Mart; Contact Center Member Service Dashboard Inventory; Contact Center Member Service Data Quality Rules</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Upstream: Genesys Cloud Contact Center; downstream: Contact Center Member Service Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>Chief Experience Officer / Salesforce Health Cloud CRM technology owner</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Salesforce Health Cloud CRM (record 18) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q23" t="str">
         <x:v>Medium</x:v>
@@ -1768,7 +1768,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>Supports member calls, CRM case management, next-best-action workflows with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="G24" t="str">
         <x:v>Contact Center and Member Service core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -1783,22 +1783,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>734 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: Average handle time by intent; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>80 interfaces or reports; 21 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Knowledge article export with duplicate and stale article flags.; performance issue: intent taxonomy drift.</x:v>
       </x:c>
       <x:c r="M24" t="str">
         <x:v>Contact Center Member Service Operational Dataset; Contact Center Member Service Analytics Mart; Contact Center Member Service Dashboard Inventory; Contact Center Member Service Data Quality Rules</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Upstream: Genesys Cloud Contact Center; downstream: Contact Center Member Service Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Chief Experience Officer / Call Transcript Lake Landing Zone technology owner</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Call Transcript Lake Landing Zone (record 19) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q24" t="str">
         <x:v>Medium</x:v>
@@ -1851,7 +1851,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue Cycle Operations Workflow Platform (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q25" t="str">
         <x:v>High</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Revenue Cycle Operations Analytics Mart (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q26" t="str">
         <x:v>Medium</x:v>
@@ -1957,7 +1957,7 @@
         <x:v>Revenue Cycle Leader / Revenue Cycle Operations Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Revenue Cycle Operations Reporting Workspace (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q27" t="str">
         <x:v>Medium</x:v>
@@ -1980,7 +1980,7 @@
         <x:v>ERP / Finance</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>Supports GL/AP/AR/budget/vendor spend reporting, close analytics, FP&amp;A dashboards with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Finance Analytics: FP&amp;A trusts 42 certified dashboards, but business-unit teams still use 300+ Excel extracts copied from legacy Tableau views.</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>GL; AP; AR; fixed assets; cost center; vendor invoice; procurement finance integration</x:v>
@@ -1995,22 +1995,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>421 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Finance Analytics users and operations volume: Certified finance dashboard adoption; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>20 interfaces or reports; 5 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.; performance issue: slow close-window dashboards.</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O28" t="str">
         <x:v>CFO / Oracle ERP Finance technology owner</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Oracle ERP Finance (record 23) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q28" t="str">
         <x:v>High</x:v>
@@ -2033,7 +2033,7 @@
         <x:v>Database / warehouse / mart</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>Finance reporting mart for GL/AP/AR/budget/vendor spend reporting and month-end close analytics.</x:v>
+        <x:v>Finance Analytics: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="G29" t="str">
         <x:v>GL/AP/AR/budget/vendor spend schemas; close reporting views; Power BI/Tableau semantic extracts</x:v>
@@ -2048,22 +2048,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>800 BI users; 1,000 finance reports; nightly refresh; month-end close spikes</x:v>
+        <x:v>Finance Analytics users and operations volume: Manual reconciliation hours per close cycle; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>Approximately 500 tables; 200 ETL jobs; 1,000 reports; 800 BI users; nightly refresh with month-end spikes</x:v>
+        <x:v>Specific scale to validate: Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.; performance issue: incomplete lineage from ERP to BI.</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>CFO / SQL Server Finance Mart technology owner</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate SQL Server Finance Mart (record 24) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q29" t="str">
         <x:v>Medium</x:v>
@@ -2086,7 +2086,7 @@
         <x:v>Database / warehouse / mart</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>Legacy finance subject area for historical finance analytics and cross-domain warehouse joins.</x:v>
+        <x:v>Finance Analytics: Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="G30" t="str">
         <x:v>Finance subject area; workload management; historical snapshots; close-cycle query workloads</x:v>
@@ -2101,22 +2101,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>Finance subject area users; warehouse query workloads; close-window peak contention</x:v>
+        <x:v>Finance Analytics users and operations volume: Close report refresh completion by 6:00 AM CT; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>Legacy subject area capacity and workload slots require validation; performance contention during close</x:v>
+        <x:v>Specific scale to validate: Finance Gold Data Product design notes for Databricks target certification.; performance issue: inconsistent vendor spend definitions.</x:v>
       </x:c>
       <x:c r="M30" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O30" t="str">
         <x:v>CFO / Netezza Finance Subject Area technology owner</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate Netezza Finance Subject Area (record 25) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q30" t="str">
         <x:v>Medium</x:v>
@@ -2139,7 +2139,7 @@
         <x:v>ETL / ELT</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>Loads ERP and workforce finance data into finance marts and reconciliation feeds.</x:v>
+        <x:v>Finance Analytics: Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="G31" t="str">
         <x:v>Oracle ERP jobs; Workday cost-center jobs; SQL Server mart loads; reconciliation jobs</x:v>
@@ -2154,22 +2154,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>200 ETL jobs tied to ERP, Workday, and finance mart loads</x:v>
+        <x:v>Finance Analytics users and operations volume: Certified finance dashboard adoption; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>Capacity requires source extract validation</x:v>
+        <x:v>Specific scale to validate: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; performance issue: slow close-window dashboards.</x:v>
       </x:c>
       <x:c r="M31" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O31" t="str">
         <x:v>CFO / Informatica Finance ETL technology owner</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate Informatica Finance ETL (record 26) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q31" t="str">
         <x:v>Medium</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>BI / reporting</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>Finance dashboards and self-service reporting for FP&amp;A, close, vendor spend, and budget analytics.</x:v>
+        <x:v>Finance Analytics: Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="G32" t="str">
         <x:v>Finance Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -2207,22 +2207,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>1,000 reports/dashboards across FP&amp;A, close, vendor spend, and budget users</x:v>
+        <x:v>Finance Analytics users and operations volume: Manual reconciliation hours per close cycle; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>Capacity requires source extract validation</x:v>
+        <x:v>Specific scale to validate: SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; performance issue: incomplete lineage from ERP to BI.</x:v>
       </x:c>
       <x:c r="M32" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>CFO / Tableau Finance Dashboards technology owner</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate Tableau Finance Dashboards (record 27) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q32" t="str">
         <x:v>Medium</x:v>
@@ -2245,7 +2245,7 @@
         <x:v>BI / reporting</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>Finance dashboards and self-service reporting for FP&amp;A, close, vendor spend, and budget analytics.</x:v>
+        <x:v>Finance Analytics: FP&amp;A trusts 42 certified dashboards, but business-unit teams still use 300+ Excel extracts copied from legacy Tableau views.</x:v>
       </x:c>
       <x:c r="G33" t="str">
         <x:v>Finance Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -2260,22 +2260,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>1,000 reports/dashboards across FP&amp;A, close, vendor spend, and budget users</x:v>
+        <x:v>Finance Analytics users and operations volume: Close report refresh completion by 6:00 AM CT; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>Capacity requires source extract validation</x:v>
+        <x:v>Specific scale to validate: Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.; performance issue: inconsistent vendor spend definitions.</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O33" t="str">
         <x:v>CFO / Power BI Finance Workspace technology owner</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate Power BI Finance Workspace (record 28) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q33" t="str">
         <x:v>Medium</x:v>
@@ -2298,7 +2298,7 @@
         <x:v>Lakehouse / data platform</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>Target Finance Gold Data Product for certified, governed finance analytics in the lakehouse.</x:v>
+        <x:v>Finance Analytics: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="G34" t="str">
         <x:v>Finance Analytics core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -2313,22 +2313,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>Target users TBD; pilot Finance Gold data product consumers</x:v>
+        <x:v>Finance Analytics users and operations volume: Certified finance dashboard adoption; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>Bronze/silver/gold layers not yet certified; capacity depends on AWS landing zone and Unity Catalog controls</x:v>
+        <x:v>Specific scale to validate: Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.; performance issue: slow close-window dashboards.</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>Finance Mart GL AP AR Subject Area; Vendor Spend and Contract Analytics Dataset; Month-End Close Reconciliation Workbook; Databricks Finance Gold Data Product</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>Upstream: Oracle ERP Finance; downstream: Vendor Spend and Contract Analytics Dataset; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Finance Analytics evidence path: Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.. Target path: Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="O34" t="str">
         <x:v>CFO / Databricks Finance Gold Data Product technology owner</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>Validate table inventory, 200 ETL jobs, 1,000 reports, 800 users, nightly refresh SLA, close-window spikes, and lineage gaps with extracts.</x:v>
+        <x:v>Validate Databricks Finance Gold Data Product (record 29) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q34" t="str">
         <x:v>Medium</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>CHRO / Workforce Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workforce Analytics Workflow Platform (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q35" t="str">
         <x:v>High</x:v>
@@ -2434,7 +2434,7 @@
         <x:v>CHRO / Workforce Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Workforce Analytics Analytics Mart (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q36" t="str">
         <x:v>Medium</x:v>
@@ -2487,7 +2487,7 @@
         <x:v>CHRO / Workforce Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Workforce Analytics Reporting Workspace (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q37" t="str">
         <x:v>Medium</x:v>
@@ -2540,7 +2540,7 @@
         <x:v>VP Quality / Clinical Quality Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Clinical Quality Analytics Workflow Platform (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>High</x:v>
@@ -2593,7 +2593,7 @@
         <x:v>VP Quality / Clinical Quality Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics Analytics Mart (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Medium</x:v>
@@ -2646,7 +2646,7 @@
         <x:v>VP Quality / Clinical Quality Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics Reporting Workspace (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Medium</x:v>
@@ -2699,7 +2699,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Claims and Payment Analytics Workflow Platform (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>High</x:v>
@@ -2752,7 +2752,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Claims and Payment Analytics Analytics Mart (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Medium</x:v>
@@ -2805,7 +2805,7 @@
         <x:v>VP Claims Analytics / Claims and Payment Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Claims and Payment Analytics Reporting Workspace (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Medium</x:v>
@@ -2858,7 +2858,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Provider Performance Analytics Workflow Platform (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>High</x:v>
@@ -2911,7 +2911,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Performance Analytics Analytics Mart (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Medium</x:v>
@@ -2964,7 +2964,7 @@
         <x:v>VP Provider Performance / Provider Performance Analytics Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P46" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Provider Performance Analytics Reporting Workspace (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q46" t="str">
         <x:v>Medium</x:v>
@@ -3017,7 +3017,7 @@
         <x:v>CDAO / Databricks on AWS Lakehouse technology owner</x:v>
       </x:c>
       <x:c r="P47" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q47" t="str">
         <x:v>High</x:v>
@@ -3070,7 +3070,7 @@
         <x:v>CDAO / Netezza Enterprise Warehouse technology owner</x:v>
       </x:c>
       <x:c r="P48" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Netezza Enterprise Warehouse (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q48" t="str">
         <x:v>Medium</x:v>
@@ -3123,7 +3123,7 @@
         <x:v>CDAO / Informatica PowerCenter technology owner</x:v>
       </x:c>
       <x:c r="P49" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Informatica PowerCenter (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q49" t="str">
         <x:v>Medium</x:v>
@@ -3176,7 +3176,7 @@
         <x:v>CDAO / Unity Catalog Target technology owner</x:v>
       </x:c>
       <x:c r="P50" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Unity Catalog Target (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q50" t="str">
         <x:v>Medium</x:v>
@@ -3229,7 +3229,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P51" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Data Governance and Data Quality Workflow Platform (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q51" t="str">
         <x:v>High</x:v>
@@ -3282,7 +3282,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P52" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Data Governance and Data Quality Analytics Mart (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q52" t="str">
         <x:v>Medium</x:v>
@@ -3335,7 +3335,7 @@
         <x:v>Chief Data Officer / Data Governance and Data Quality Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P53" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality Reporting Workspace (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q53" t="str">
         <x:v>Medium</x:v>
@@ -3343,7 +3343,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>Agent Assist and Next Best Action Workflow Platform</x:v>
+        <x:v>Member Service Agent Assist Workbench</x:v>
       </x:c>
       <x:c r="B54" t="str">
         <x:v>Member Experience</x:v>
@@ -3358,7 +3358,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F54" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="G54" t="str">
         <x:v>Agent Assist and Next Best Action core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3373,22 +3373,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>729 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: Average handle time by intent; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>20 interfaces or reports; 5 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Knowledge article export with duplicate and stale article flags.; performance issue: intent taxonomy drift.</x:v>
       </x:c>
       <x:c r="M54" t="str">
         <x:v>Agent Assist Next Best Action Operational Dataset; Agent Assist Next Best Action Analytics Mart; Agent Assist Next Best Action Dashboard Inventory; Agent Assist Next Best Action Data Quality Rules</x:v>
       </x:c>
       <x:c r="N54" t="str">
-        <x:v>Upstream: Agent Assist and Next Best Action Workflow Platform; downstream: Agent Assist Next Best Action Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O54" t="str">
         <x:v>VP Contact Center / Agent Assist and Next Best Action Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P54" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Member Service Agent Assist Workbench (record 49) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q54" t="str">
         <x:v>High</x:v>
@@ -3396,7 +3396,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>Agent Assist and Next Best Action Analytics Mart</x:v>
+        <x:v>Call Intent and Transcript Analytics Mart</x:v>
       </x:c>
       <x:c r="B55" t="str">
         <x:v>Member Experience</x:v>
@@ -3411,7 +3411,7 @@
         <x:v>Database / warehouse / mart</x:v>
       </x:c>
       <x:c r="F55" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="G55" t="str">
         <x:v>Agent Assist and Next Best Action core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3426,22 +3426,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>904 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: First contact resolution for claims-status calls; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>50 interfaces or reports; 13 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.; performance issue: CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="M55" t="str">
         <x:v>Agent Assist Next Best Action Operational Dataset; Agent Assist Next Best Action Analytics Mart; Agent Assist Next Best Action Dashboard Inventory; Agent Assist Next Best Action Data Quality Rules</x:v>
       </x:c>
       <x:c r="N55" t="str">
-        <x:v>Upstream: Agent Assist and Next Best Action Workflow Platform; downstream: Agent Assist Next Best Action Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O55" t="str">
         <x:v>VP Contact Center / Agent Assist and Next Best Action Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P55" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Call Intent and Transcript Analytics Mart (record 50) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q55" t="str">
         <x:v>Medium</x:v>
@@ -3449,7 +3449,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>Agent Assist and Next Best Action Reporting Workspace</x:v>
+        <x:v>Next-Best-Action Rules and Knowledge Workspace</x:v>
       </x:c>
       <x:c r="B56" t="str">
         <x:v>Member Experience</x:v>
@@ -3464,7 +3464,7 @@
         <x:v>Enterprise platform</x:v>
       </x:c>
       <x:c r="F56" t="str">
-        <x:v>Supports agent assist, call summarization, intent detection, guided resolution with operational workflow, reporting, controls, or modernization capability.</x:v>
+        <x:v>Agent Assist / Member Service: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="G56" t="str">
         <x:v>Agent Assist and Next Best Action core module; exception queue; audit trail; reporting/export module; integration endpoints</x:v>
@@ -3479,22 +3479,22 @@
         <x:v>Dev; Test; UAT; Prod where applicable; lower-environment completeness requires validation</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>1079 named/indirect users; transaction volume requires client extract</x:v>
+        <x:v>Agent Assist / Member Service users and operations volume: After-call work minutes per agent shift; source extract required for exact count.</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>80 interfaces or reports; 21 batch/API jobs; platform capacity and SLA require validation</x:v>
+        <x:v>Specific scale to validate: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; performance issue: stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="M56" t="str">
         <x:v>Agent Assist Next Best Action Operational Dataset; Agent Assist Next Best Action Analytics Mart; Agent Assist Next Best Action Dashboard Inventory; Agent Assist Next Best Action Data Quality Rules</x:v>
       </x:c>
       <x:c r="N56" t="str">
-        <x:v>Upstream: Agent Assist and Next Best Action Workflow Platform; downstream: Agent Assist Next Best Action Analytics Mart; BI/analytics consumers; Databricks on AWS Lakehouse target where applicable</x:v>
+        <x:v>Agent Assist / Member Service evidence path: Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.. Target path: audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="O56" t="str">
         <x:v>VP Contact Center / Agent Assist and Next Best Action Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P56" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Next-Best-Action Rules and Knowledge Workspace (record 51) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="Q56" t="str">
         <x:v>Medium</x:v>
@@ -3547,7 +3547,7 @@
         <x:v>CDAO / Epic Clarity technology owner</x:v>
       </x:c>
       <x:c r="P57" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm Epic Clarity (record 52) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q57" t="str">
         <x:v>High</x:v>
@@ -3600,7 +3600,7 @@
         <x:v>CDAO / Claims Administration Platform technology owner</x:v>
       </x:c>
       <x:c r="P58" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for Claims Administration Platform (record 53), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q58" t="str">
         <x:v>Medium</x:v>
@@ -3653,7 +3653,7 @@
         <x:v>CDAO / Pharmacy Claims Platform technology owner</x:v>
       </x:c>
       <x:c r="P59" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Pharmacy Claims Platform (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q59" t="str">
         <x:v>Medium</x:v>
@@ -3706,7 +3706,7 @@
         <x:v>CDAO / Databricks Clinical Claims Lakehouse technology owner</x:v>
       </x:c>
       <x:c r="P60" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks Clinical Claims Lakehouse (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q60" t="str">
         <x:v>Medium</x:v>
@@ -3759,7 +3759,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P61" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline Workflow Platform (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q61" t="str">
         <x:v>High</x:v>
@@ -3812,7 +3812,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P62" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Analytics Mart (record 57) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q62" t="str">
         <x:v>Medium</x:v>
@@ -3865,7 +3865,7 @@
         <x:v>CIO / CFO / IT Budget and Tower Baseline Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P63" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Reporting Workspace (record 58), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q63" t="str">
         <x:v>Medium</x:v>
@@ -3918,7 +3918,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Workflow Platform technology owner</x:v>
       </x:c>
       <x:c r="P64" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization Workflow Platform (record 59) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q64" t="str">
         <x:v>High</x:v>
@@ -3971,7 +3971,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Analytics Mart technology owner</x:v>
       </x:c>
       <x:c r="P65" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Analytics Mart (record 60) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q65" t="str">
         <x:v>Medium</x:v>
@@ -4024,7 +4024,7 @@
         <x:v>Chief Procurement Officer / Vendor and Contract Optimization Reporting Workspace technology owner</x:v>
       </x:c>
       <x:c r="P66" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Vendor and Contract Optimization Reporting Workspace (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q66" t="str">
         <x:v>Medium</x:v>
@@ -4077,7 +4077,7 @@
         <x:v>CTO / ServiceNow CMDB technology owner</x:v>
       </x:c>
       <x:c r="P67" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm ServiceNow CMDB (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q67" t="str">
         <x:v>High</x:v>
@@ -4130,7 +4130,7 @@
         <x:v>CTO / VMware Data Center Cluster technology owner</x:v>
       </x:c>
       <x:c r="P68" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Attach client evidence for VMware Data Center Cluster (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="Q68" t="str">
         <x:v>Medium</x:v>
@@ -4183,7 +4183,7 @@
         <x:v>CTO / AWS Analytics Landing Zone technology owner</x:v>
       </x:c>
       <x:c r="P69" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Reconcile AWS Analytics Landing Zone (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="Q69" t="str">
         <x:v>Medium</x:v>
@@ -4236,7 +4236,7 @@
         <x:v>VP IT Operations / ServiceNow ITSM technology owner</x:v>
       </x:c>
       <x:c r="P70" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow ITSM (record 65) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="Q70" t="str">
         <x:v>High</x:v>
@@ -4289,7 +4289,7 @@
         <x:v>VP IT Operations / Datadog Observability technology owner</x:v>
       </x:c>
       <x:c r="P71" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Validate Datadog Observability (record 66) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for applications systems.</x:v>
       </x:c>
       <x:c r="Q71" t="str">
         <x:v>Medium</x:v>
@@ -4342,7 +4342,7 @@
         <x:v>VP IT Operations / PagerDuty Incident Response technology owner</x:v>
       </x:c>
       <x:c r="P72" t="str">
-        <x:v>Confirm version, interface inventory, active users, lifecycle status, DR tier, and source-of-truth boundaries.</x:v>
+        <x:v>Confirm PagerDuty Incident Response (record 67) current-vs-target status, module boundary, volume baseline, and relationship links before this applications systems record is used downstream.</x:v>
       </x:c>
       <x:c r="Q72" t="str">
         <x:v>Medium</x:v>
@@ -4375,7 +4375,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48f25fe56bbf445c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dc35dbd24584756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4494,7 +4494,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ef2c0106dbc48a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9adde448674846"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5175,7 +5175,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R468b0f9197c049db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7aded4021f4c4d91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5269,7 +5269,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e5ebc9efe244a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb58e432488a4ca9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5379,7 +5379,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R889dddb587c24753"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf9f6c230f34597"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5509,7 +5509,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bf9815f90854812"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b143b8555624c99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5595,7 +5595,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43c06a5ee27f48b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R301b16dc710842a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>